--- a/data/trans_orig/ProbViv_estruc-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/ProbViv_estruc-Provincia-trans_orig.xlsx
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>578</t>
+          <t>548</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6930</t>
+          <t>5883</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,46%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1823</t>
+          <t>1930</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>10760</t>
+          <t>10126</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>13,56%</t>
+          <t>12,76%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3321</t>
+          <t>3188</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>13345</t>
+          <t>13557</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>8,88%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>66352</t>
+          <t>67399</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>72704</t>
+          <t>72734</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>90,54%</t>
+          <t>91,97%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,21%</t>
+          <t>99,25%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>68606</t>
+          <t>69240</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>77543</t>
+          <t>77436</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>86,44%</t>
+          <t>87,24%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,7%</t>
+          <t>97,57%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>139303</t>
+          <t>139091</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>149327</t>
+          <t>149460</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>91,26%</t>
+          <t>91,12%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,82%</t>
+          <t>97,91%</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6468</t>
+          <t>7057</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>26984</t>
+          <t>26765</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>21,14%</t>
+          <t>20,97%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6631</t>
+          <t>6577</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>19135</t>
+          <t>18231</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>15,0%</t>
+          <t>14,29%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>17455</t>
+          <t>17011</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>39021</t>
+          <t>38681</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>15,29%</t>
+          <t>15,15%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>100670</t>
+          <t>100889</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>121186</t>
+          <t>120597</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>78,86%</t>
+          <t>79,03%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>94,93%</t>
+          <t>94,47%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>108461</t>
+          <t>109365</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>120965</t>
+          <t>121019</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>85,0%</t>
+          <t>85,71%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,8%</t>
+          <t>94,85%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>216229</t>
+          <t>216569</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>237795</t>
+          <t>238239</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>84,71%</t>
+          <t>84,85%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,16%</t>
+          <t>93,34%</t>
         </is>
       </c>
     </row>
@@ -1416,12 +1416,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4701</t>
+          <t>4319</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>13122</t>
+          <t>12388</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1431,12 +1431,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>22,52%</t>
+          <t>21,26%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3265</t>
+          <t>3077</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>10894</t>
+          <t>10536</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>16,22%</t>
+          <t>15,69%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>8853</t>
+          <t>9474</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>20377</t>
+          <t>20378</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>7,55%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -1529,12 +1529,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>45146</t>
+          <t>45880</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>53567</t>
+          <t>53949</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1544,12 +1544,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>77,48%</t>
+          <t>78,74%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>91,93%</t>
+          <t>92,59%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1564,12 +1564,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>56269</t>
+          <t>56627</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>63898</t>
+          <t>64086</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1579,12 +1579,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>83,78%</t>
+          <t>84,31%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,14%</t>
+          <t>95,42%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>105054</t>
+          <t>105053</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>116578</t>
+          <t>115957</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>92,94%</t>
+          <t>92,45%</t>
         </is>
       </c>
     </row>
@@ -1759,12 +1759,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1054</t>
+          <t>1148</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7348</t>
+          <t>7684</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,63%</t>
+          <t>11,11%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1475</t>
+          <t>1374</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>11978</t>
+          <t>11461</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>15,33%</t>
+          <t>14,67%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3947</t>
+          <t>3736</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>16543</t>
+          <t>15371</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,23%</t>
+          <t>10,44%</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>61796</t>
+          <t>61460</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>68090</t>
+          <t>67996</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,12 +1887,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>89,37%</t>
+          <t>88,89%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,48%</t>
+          <t>98,34%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>66156</t>
+          <t>66673</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>76659</t>
+          <t>76760</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>84,67%</t>
+          <t>85,33%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>98,24%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>130735</t>
+          <t>131907</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>143331</t>
+          <t>143542</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>88,77%</t>
+          <t>89,56%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,32%</t>
+          <t>97,46%</t>
         </is>
       </c>
     </row>
@@ -2107,7 +2107,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2267</t>
+          <t>2080</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2137,12 +2137,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>566</t>
+          <t>564</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>5784</t>
+          <t>5462</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2152,12 +2152,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>14,2%</t>
+          <t>13,41%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2172,12 +2172,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>586</t>
+          <t>747</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>5796</t>
+          <t>5822</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2187,12 +2187,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>7,74%</t>
         </is>
       </c>
     </row>
@@ -2215,7 +2215,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>32246</t>
+          <t>32433</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2230,7 +2230,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>93,43%</t>
+          <t>93,97%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2250,12 +2250,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>34935</t>
+          <t>35257</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>40153</t>
+          <t>40155</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2265,12 +2265,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>85,8%</t>
+          <t>86,59%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,61%</t>
+          <t>98,62%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2285,12 +2285,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>69436</t>
+          <t>69410</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>74646</t>
+          <t>74485</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2300,12 +2300,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>92,3%</t>
+          <t>92,26%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,22%</t>
+          <t>99,01%</t>
         </is>
       </c>
     </row>
@@ -2445,12 +2445,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1277</t>
+          <t>1533</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7409</t>
+          <t>7357</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2460,47 +2460,47 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
+          <t>3,32%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>15,94%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>3840</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>1556</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>7553</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>6,83%</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
           <t>2,77%</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>16,05%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>3840</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>1656</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>7578</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>6,83%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>2,95%</t>
-        </is>
-      </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>13,49%</t>
+          <t>13,44%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2515,12 +2515,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>4112</t>
+          <t>3941</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>11940</t>
+          <t>12231</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>11,67%</t>
+          <t>11,95%</t>
         </is>
       </c>
     </row>
@@ -2558,12 +2558,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>38758</t>
+          <t>38810</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>44890</t>
+          <t>44634</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2573,49 +2573,49 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>83,95%</t>
+          <t>84,06%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
+          <t>96,68%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>52346</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>48633</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>54630</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>93,17%</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>86,56%</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
           <t>97,23%</t>
         </is>
       </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>86</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>52346</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>48608</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>54530</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>93,17%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>86,51%</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>97,05%</t>
-        </is>
-      </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
           <t>159</t>
@@ -2628,12 +2628,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>90413</t>
+          <t>90122</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>98241</t>
+          <t>98412</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2643,12 +2643,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>88,33%</t>
+          <t>88,05%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>95,98%</t>
+          <t>96,15%</t>
         </is>
       </c>
     </row>
@@ -2788,12 +2788,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>7339</t>
+          <t>7605</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>21358</t>
+          <t>20840</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2803,12 +2803,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>17,15%</t>
+          <t>16,74%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2823,12 +2823,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>9999</t>
+          <t>9554</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>24292</t>
+          <t>23463</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2838,12 +2838,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>15,67%</t>
+          <t>15,13%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2858,12 +2858,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>19963</t>
+          <t>20038</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>38999</t>
+          <t>39782</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2873,12 +2873,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>13,95%</t>
+          <t>14,23%</t>
         </is>
       </c>
     </row>
@@ -2901,12 +2901,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>103150</t>
+          <t>103668</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>117169</t>
+          <t>116903</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2916,12 +2916,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>82,85%</t>
+          <t>83,26%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>94,11%</t>
+          <t>93,89%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2936,12 +2936,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>130777</t>
+          <t>131606</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>145070</t>
+          <t>145515</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2951,12 +2951,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>84,33%</t>
+          <t>84,87%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>93,55%</t>
+          <t>93,84%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2971,12 +2971,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>240578</t>
+          <t>239795</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>259614</t>
+          <t>259539</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2986,12 +2986,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>86,05%</t>
+          <t>85,77%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>92,86%</t>
+          <t>92,83%</t>
         </is>
       </c>
     </row>
@@ -3131,12 +3131,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>13272</t>
+          <t>13156</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>27215</t>
+          <t>26420</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3146,12 +3146,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>10,08%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>20,68%</t>
+          <t>20,07%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3166,12 +3166,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>16416</t>
+          <t>16874</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>32955</t>
+          <t>33865</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3181,12 +3181,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>10,76%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>21,02%</t>
+          <t>21,6%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>34419</t>
+          <t>33953</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>55255</t>
+          <t>53697</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3216,12 +3216,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>11,93%</t>
+          <t>11,77%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>19,16%</t>
+          <t>18,62%</t>
         </is>
       </c>
     </row>
@@ -3244,12 +3244,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>104404</t>
+          <t>105199</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>118347</t>
+          <t>118463</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3259,12 +3259,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>79,32%</t>
+          <t>79,93%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>89,92%</t>
+          <t>90,0%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>123840</t>
+          <t>122930</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>140379</t>
+          <t>139921</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3294,12 +3294,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>78,98%</t>
+          <t>78,4%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>89,53%</t>
+          <t>89,24%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>233159</t>
+          <t>234717</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>253995</t>
+          <t>254461</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3329,12 +3329,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>80,84%</t>
+          <t>81,38%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>88,07%</t>
+          <t>88,23%</t>
         </is>
       </c>
     </row>
@@ -3474,12 +3474,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>51383</t>
+          <t>50689</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>83388</t>
+          <t>81698</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>12,54%</t>
+          <t>12,28%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3509,12 +3509,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>59503</t>
+          <t>58030</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>88982</t>
+          <t>90503</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3524,12 +3524,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>11,69%</t>
+          <t>11,89%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3544,12 +3544,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>117506</t>
+          <t>117272</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>160601</t>
+          <t>159766</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3559,12 +3559,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>8,22%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>11,26%</t>
+          <t>11,2%</t>
         </is>
       </c>
     </row>
@@ -3587,12 +3587,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>581768</t>
+          <t>583458</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>613773</t>
+          <t>614467</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3602,12 +3602,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>87,46%</t>
+          <t>87,72%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>92,28%</t>
+          <t>92,38%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3622,12 +3622,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>672046</t>
+          <t>670525</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>701525</t>
+          <t>702998</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3637,12 +3637,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>88,31%</t>
+          <t>88,11%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>92,18%</t>
+          <t>92,37%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3657,12 +3657,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1265583</t>
+          <t>1266418</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1308678</t>
+          <t>1308912</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3672,12 +3672,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>88,74%</t>
+          <t>88,8%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>91,76%</t>
+          <t>91,78%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/ProbViv_estruc-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/ProbViv_estruc-Provincia-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>3806</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>1388</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>7994</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>5,93%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>2,16%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>12,46%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>2244</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>548</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>5883</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>3,06%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0,75%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>8,03%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>4968</t>
+          <t>1841</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1930</t>
+          <t>472</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>10126</t>
+          <t>5024</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,76%</t>
+          <t>8,9%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>7212</t>
+          <t>5647</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3188</t>
+          <t>2636</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>13557</t>
+          <t>10872</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,88%</t>
+          <t>9,01%</t>
         </is>
       </c>
     </row>
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>60339</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>56151</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>62757</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>94,07%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>87,54%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>97,84%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>93</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>71038</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>67399</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>72734</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>96,94%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>91,97%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>99,25%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>96</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>74398</t>
+          <t>54640</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>69240</t>
+          <t>51457</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>77436</t>
+          <t>56009</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>93,74%</t>
+          <t>96,74%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>87,24%</t>
+          <t>91,1%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,57%</t>
+          <t>99,16%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>145436</t>
+          <t>114979</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>139091</t>
+          <t>109754</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>149460</t>
+          <t>117990</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>95,28%</t>
+          <t>95,32%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>91,12%</t>
+          <t>90,99%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,91%</t>
+          <t>97,81%</t>
         </is>
       </c>
     </row>
@@ -946,57 +946,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>64145</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>64145</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>64145</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>96</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>73282</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>73282</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>73282</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>102</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>79366</t>
+          <t>56481</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>79366</t>
+          <t>56481</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>79366</t>
+          <t>56481</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>152648</t>
+          <t>120626</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>152648</t>
+          <t>120626</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>152648</t>
+          <t>120626</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1063,72 +1063,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>9924</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>5791</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>16938</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>8,57%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>5,0%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>14,62%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>15746</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>7057</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>26765</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>12,33%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>5,53%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>20,97%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>11403</t>
+          <t>13553</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6577</t>
+          <t>8452</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>18231</t>
+          <t>20797</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>13,37%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>14,29%</t>
+          <t>20,51%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>27149</t>
+          <t>23477</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>17011</t>
+          <t>17054</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>38681</t>
+          <t>32869</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>10,64%</t>
+          <t>10,81%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>7,85%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>15,15%</t>
+          <t>15,13%</t>
         </is>
       </c>
     </row>
@@ -1176,72 +1176,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>139</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>105911</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>98897</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>110044</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>91,43%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>85,38%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>95,0%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>123</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>111908</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>100889</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>120597</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>87,67%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>79,03%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>94,47%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>139</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>116193</t>
+          <t>87842</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>109365</t>
+          <t>80598</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>121019</t>
+          <t>92943</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>91,06%</t>
+          <t>86,63%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>85,71%</t>
+          <t>79,49%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,85%</t>
+          <t>91,66%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>228101</t>
+          <t>193754</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>216569</t>
+          <t>184362</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>238239</t>
+          <t>200177</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>89,36%</t>
+          <t>89,19%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>84,85%</t>
+          <t>84,87%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,34%</t>
+          <t>92,15%</t>
         </is>
       </c>
     </row>
@@ -1289,57 +1289,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>156</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>115835</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>115835</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>115835</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>142</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>127654</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>127654</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>127654</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>156</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>127596</t>
+          <t>101395</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>127596</t>
+          <t>101395</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>127596</t>
+          <t>101395</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>255250</t>
+          <t>217231</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>255250</t>
+          <t>217231</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>255250</t>
+          <t>217231</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1406,72 +1406,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>5476</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>2773</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>9487</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>9,22%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>4,67%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>15,98%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>8110</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>4319</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>12388</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>13,92%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>7,41%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>21,26%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>6270</t>
+          <t>8157</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3077</t>
+          <t>4623</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>10536</t>
+          <t>12859</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>14,42%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>15,69%</t>
+          <t>22,74%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>14381</t>
+          <t>13633</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>9474</t>
+          <t>8648</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>20378</t>
+          <t>19126</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>11,46%</t>
+          <t>11,76%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>16,25%</t>
+          <t>16,5%</t>
         </is>
       </c>
     </row>
@@ -1519,72 +1519,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>53901</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>49890</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>56604</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>90,78%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>84,02%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>95,33%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>84</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>50158</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>45880</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>53949</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>86,08%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>78,74%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>92,59%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>91</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>60893</t>
+          <t>48401</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>56627</t>
+          <t>43699</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>64086</t>
+          <t>51935</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>90,66%</t>
+          <t>85,58%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>84,31%</t>
+          <t>77,26%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,42%</t>
+          <t>91,83%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>111050</t>
+          <t>102303</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>105053</t>
+          <t>96810</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>115957</t>
+          <t>107288</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>88,54%</t>
+          <t>88,24%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>83,75%</t>
+          <t>83,5%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>92,45%</t>
+          <t>92,54%</t>
         </is>
       </c>
     </row>
@@ -1632,57 +1632,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>59377</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>59377</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>59377</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>97</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>58268</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>58268</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>58268</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>101</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>67163</t>
+          <t>56558</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>67163</t>
+          <t>56558</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>67163</t>
+          <t>56558</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>125431</t>
+          <t>115936</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>125431</t>
+          <t>115936</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>125431</t>
+          <t>115936</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,32 +1754,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3258</t>
+          <t>3830</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1148</t>
+          <t>1145</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7684</t>
+          <t>11127</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,11%</t>
+          <t>15,42%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,32 +1789,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>4547</t>
+          <t>3207</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1374</t>
+          <t>1086</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>11461</t>
+          <t>7920</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>14,67%</t>
+          <t>11,35%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>7804</t>
+          <t>7036</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3736</t>
+          <t>3187</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>15371</t>
+          <t>14298</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>10,44%</t>
+          <t>10,07%</t>
         </is>
       </c>
     </row>
@@ -1862,72 +1862,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>68332</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>61035</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>71017</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>94,69%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>84,58%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>98,41%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>88</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>65886</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>61460</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>67996</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>95,29%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>88,89%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>98,34%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>73587</t>
+          <t>66561</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>66673</t>
+          <t>61848</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>76760</t>
+          <t>68682</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>94,18%</t>
+          <t>95,4%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>85,33%</t>
+          <t>88,65%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,24%</t>
+          <t>98,44%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>139474</t>
+          <t>134894</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>131907</t>
+          <t>127632</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>143542</t>
+          <t>138743</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>94,7%</t>
+          <t>95,04%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>89,56%</t>
+          <t>89,93%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,46%</t>
+          <t>97,75%</t>
         </is>
       </c>
     </row>
@@ -1975,57 +1975,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>72162</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>72162</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>72162</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>93</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>69144</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>69144</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>69144</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>78134</t>
+          <t>69768</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>78134</t>
+          <t>69768</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>78134</t>
+          <t>69768</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>147278</t>
+          <t>141930</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>147278</t>
+          <t>141930</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>147278</t>
+          <t>141930</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2092,72 +2092,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>1926</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>483</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>5308</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>4,87%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>1,22%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>13,41%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>403</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>541</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>2080</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>1,17%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>2770</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>1,52%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>6,03%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>2017</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>564</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>5462</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>4,95%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>1,38%</t>
-        </is>
-      </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>13,41%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>2420</t>
+          <t>2467</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>747</t>
+          <t>590</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>5822</t>
+          <t>5915</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>7,87%</t>
         </is>
       </c>
     </row>
@@ -2205,74 +2205,74 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>37653</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>34271</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>39096</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>95,13%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>86,59%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>98,78%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>67</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>34110</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>32433</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>34513</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>98,83%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>93,97%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>35067</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>32838</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>35608</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>98,48%</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>92,22%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>38702</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>35257</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>40155</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>95,05%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>86,59%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>98,62%</t>
-        </is>
-      </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
           <t>135</t>
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>72812</t>
+          <t>72720</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>69410</t>
+          <t>69272</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>74485</t>
+          <t>74597</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>96,78%</t>
+          <t>96,72%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>92,26%</t>
+          <t>92,13%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,01%</t>
+          <t>99,21%</t>
         </is>
       </c>
     </row>
@@ -2318,57 +2318,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>39579</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>39579</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>39579</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>68</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>34513</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>34513</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>34513</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>40719</t>
+          <t>35608</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>40719</t>
+          <t>35608</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>40719</t>
+          <t>35608</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>75232</t>
+          <t>75187</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>75232</t>
+          <t>75187</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>75232</t>
+          <t>75187</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2435,72 +2435,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>3280</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>1347</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>6441</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>6,7%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>2,75%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>13,16%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>3409</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>1533</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>7357</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>7,38%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>3,32%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>15,94%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>3840</t>
+          <t>3528</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1556</t>
+          <t>1289</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>7553</t>
+          <t>7209</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>13,44%</t>
+          <t>15,75%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,32 +2510,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>7249</t>
+          <t>6808</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>3941</t>
+          <t>3595</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>12231</t>
+          <t>11454</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>11,95%</t>
+          <t>12,09%</t>
         </is>
       </c>
     </row>
@@ -2548,72 +2548,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>45662</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>42501</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>47595</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>93,3%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>86,84%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>97,25%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>73</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>42758</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>38810</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>44634</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>92,62%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>84,06%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>96,68%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>86</t>
-        </is>
-      </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>52346</t>
+          <t>42238</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>48633</t>
+          <t>38557</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>54630</t>
+          <t>44477</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>93,17%</t>
+          <t>92,29%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>86,56%</t>
+          <t>84,25%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>97,23%</t>
+          <t>97,18%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,32 +2623,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>95104</t>
+          <t>87900</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>90122</t>
+          <t>83254</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>98412</t>
+          <t>91113</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>92,92%</t>
+          <t>92,81%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>88,05%</t>
+          <t>87,91%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>96,15%</t>
+          <t>96,2%</t>
         </is>
       </c>
     </row>
@@ -2661,57 +2661,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>48942</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>48942</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>48942</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>79</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>46167</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>46167</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>46167</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>93</t>
-        </is>
-      </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>56186</t>
+          <t>45766</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>56186</t>
+          <t>45766</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>56186</t>
+          <t>45766</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>102353</t>
+          <t>94708</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>102353</t>
+          <t>94708</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>102353</t>
+          <t>94708</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2778,72 +2778,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>14725</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>9258</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>22798</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>10,49%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>6,59%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>16,24%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>12322</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>7605</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>20840</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>9,9%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>6,11%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>16,74%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>15831</t>
+          <t>10512</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>9554</t>
+          <t>6374</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>23463</t>
+          <t>16527</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>8,58%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>15,13%</t>
+          <t>13,49%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,32 +2853,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>28153</t>
+          <t>25237</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>20038</t>
+          <t>17748</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>39782</t>
+          <t>34226</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>9,6%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>14,23%</t>
+          <t>13,02%</t>
         </is>
       </c>
     </row>
@@ -2891,72 +2891,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>157</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>125686</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>117613</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>131153</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>89,51%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>83,76%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>93,41%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>159</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>112186</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>103668</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>116903</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>90,1%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>83,26%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>93,89%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>157</t>
-        </is>
-      </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>139238</t>
+          <t>112017</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>131606</t>
+          <t>106002</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>145515</t>
+          <t>116155</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>89,79%</t>
+          <t>91,42%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>84,87%</t>
+          <t>86,51%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>93,84%</t>
+          <t>94,8%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2966,32 +2966,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>251424</t>
+          <t>237703</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>239795</t>
+          <t>228714</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>259539</t>
+          <t>245192</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>89,93%</t>
+          <t>90,4%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>85,77%</t>
+          <t>86,98%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>92,83%</t>
+          <t>93,25%</t>
         </is>
       </c>
     </row>
@@ -3004,57 +3004,57 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>177</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>140411</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>140411</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>140411</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>176</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>124508</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>124508</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>124508</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>177</t>
-        </is>
-      </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>155069</t>
+          <t>122529</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>155069</t>
+          <t>122529</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>155069</t>
+          <t>122529</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3079,17 +3079,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>279577</t>
+          <t>262940</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>279577</t>
+          <t>262940</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>279577</t>
+          <t>262940</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3121,72 +3121,72 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>25218</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>17619</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>34576</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>15,82%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>11,05%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>21,69%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
           <t>30</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>19313</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>13156</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>26420</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>14,67%</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>10,0%</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>20,07%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>24453</t>
+          <t>20017</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>16874</t>
+          <t>13679</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>33865</t>
+          <t>28910</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>15,6%</t>
+          <t>14,25%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>9,74%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>21,6%</t>
+          <t>20,58%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3196,32 +3196,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>43766</t>
+          <t>45235</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>33953</t>
+          <t>35654</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>53697</t>
+          <t>58254</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>15,17%</t>
+          <t>15,08%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>11,77%</t>
+          <t>11,89%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>18,62%</t>
+          <t>19,42%</t>
         </is>
       </c>
     </row>
@@ -3234,72 +3234,72 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>177</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>134203</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>124845</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>141802</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>84,18%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>78,31%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>88,95%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
           <t>161</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>112306</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>105199</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>118463</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>85,33%</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>79,93%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>90,0%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>177</t>
-        </is>
-      </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>132342</t>
+          <t>120480</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>122930</t>
+          <t>111587</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>139921</t>
+          <t>126818</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>84,4%</t>
+          <t>85,75%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>78,4%</t>
+          <t>79,42%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>89,24%</t>
+          <t>90,26%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3309,32 +3309,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>244648</t>
+          <t>254683</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>234717</t>
+          <t>241664</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>254461</t>
+          <t>264264</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>84,83%</t>
+          <t>84,92%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>81,38%</t>
+          <t>80,58%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>88,23%</t>
+          <t>88,11%</t>
         </is>
       </c>
     </row>
@@ -3347,57 +3347,57 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>208</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>159421</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>159421</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>159421</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>191</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>131619</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>131619</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>131619</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>208</t>
-        </is>
-      </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>156795</t>
+          <t>140497</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>156795</t>
+          <t>140497</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>156795</t>
+          <t>140497</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3422,17 +3422,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>288414</t>
+          <t>299918</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>288414</t>
+          <t>299918</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>288414</t>
+          <t>299918</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3464,72 +3464,72 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>68184</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>54905</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>83074</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>9,74%</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>7,84%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>11,87%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
           <t>94</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>64805</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>50689</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>81698</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>9,74%</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>7,62%</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>12,28%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>99</t>
-        </is>
-      </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>73329</t>
+          <t>61356</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>58030</t>
+          <t>49795</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>90503</t>
+          <t>75604</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>9,76%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>7,92%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>11,89%</t>
+          <t>12,03%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3539,32 +3539,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>138135</t>
+          <t>129540</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>117272</t>
+          <t>112229</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>159766</t>
+          <t>148939</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>9,75%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>11,21%</t>
         </is>
       </c>
     </row>
@@ -3577,72 +3577,72 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>877</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>631688</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>616798</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>644967</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>90,26%</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>88,13%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>92,16%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
           <t>848</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>600351</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>583458</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>614467</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>90,26%</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>87,72%</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>92,38%</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>877</t>
-        </is>
-      </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>687699</t>
+          <t>567247</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>670525</t>
+          <t>552999</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>702998</t>
+          <t>578808</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>90,36%</t>
+          <t>90,24%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>88,11%</t>
+          <t>87,97%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>92,37%</t>
+          <t>92,08%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3652,32 +3652,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>1288049</t>
+          <t>1198935</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1266418</t>
+          <t>1179536</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1308912</t>
+          <t>1216246</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>90,31%</t>
+          <t>90,25%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>88,8%</t>
+          <t>88,79%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>91,78%</t>
+          <t>91,55%</t>
         </is>
       </c>
     </row>
@@ -3690,57 +3690,57 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>976</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>699872</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>699872</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>699872</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
           <t>942</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>665156</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>665156</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>665156</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>976</t>
-        </is>
-      </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>761028</t>
+          <t>628603</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>761028</t>
+          <t>628603</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>761028</t>
+          <t>628603</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3765,17 +3765,17 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>1426184</t>
+          <t>1328475</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1426184</t>
+          <t>1328475</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1426184</t>
+          <t>1328475</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
